--- a/artfynd/A 38013-2022 artfynd.xlsx
+++ b/artfynd/A 38013-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127858834</v>
       </c>
       <c r="B2" t="n">
-        <v>56585</v>
+        <v>56612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38013-2022 artfynd.xlsx
+++ b/artfynd/A 38013-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127858834</v>
       </c>
       <c r="B2" t="n">
-        <v>56618</v>
+        <v>56620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38013-2022 artfynd.xlsx
+++ b/artfynd/A 38013-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127858834</v>
+        <v>97618990</v>
       </c>
       <c r="B2" t="n">
-        <v>56620</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100053</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>269 73 Båstads kommun, Sk</t>
+          <t>Hålehallstugan, 225 m ONO, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>367019</v>
+        <v>367037</v>
       </c>
       <c r="R2" t="n">
-        <v>6248268</v>
+        <v>6248341</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:32</t>
+          <t>2019-12-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:32</t>
+          <t>2019-12-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,18 +757,410 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>slänt i granskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>humus</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>W-RÅk-68066</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Richard Åkesson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Richard Åkesson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Projekt Skånes mossor</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>97618988</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hålehallstugan, 225 m ONO, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>367037</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6248341</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Båstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Förslöv</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-12-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-12-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>slänt i granskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>humus, barr</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>W-RÅk-68068</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Richard Åkesson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Richard Åkesson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Projekt Skånes mossor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97618986</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hålehallstugan, 225 m ONO, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>367037</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6248341</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Båstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Förslöv</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-12-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-12-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>slänt i granskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>humus</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>W-RÅk-68070</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Richard Åkesson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Richard Åkesson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Projekt Skånes mossor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127858834</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56845</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>269 73 Båstads kommun, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>367019</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6248268</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Båstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Förslöv</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Johan Möller</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>

--- a/artfynd/A 38013-2022 artfynd.xlsx
+++ b/artfynd/A 38013-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97618990</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97618988</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,6 +1055,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97618986</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1165,8 +1185,19 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127858834</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>